--- a/web/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/web/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -31026,7 +31026,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>19981000</v>
       </c>
       <c r="I452" s="5" t="n">
-        <v>29867</v>
+        <v>29822</v>
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>19981000</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>29867</v>
+        <v>29822</v>
       </c>
       <c r="M452" s="3" t="inlineStr">
         <is>
@@ -39297,9 +39297,9 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>A | 669呎 (3房)
+          <t>A | 670呎 (3房)
 $1998万
-$29,867/呎
+$29,822/呎
 (25年-10月-03日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/web/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>17293000</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>30392</v>
+        <v>30445</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>17293000</v>
       </c>
       <c r="L459" s="5" t="n">
-        <v>30392</v>
+        <v>30445</v>
       </c>
       <c r="M459" s="3" t="inlineStr">
         <is>
@@ -39392,9 +39392,9 @@
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>C | 569呎 (3房)
+          <t>C | 568呎 (3房)
 $1729万
-$30,392/呎
+$30,445/呎
 (26年-01月-12日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-维港．湾畔第1B期.xlsx
+++ b/web/files/九龙-启德-维港．湾畔第1B期.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35189,7 +35189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35209,7 +35209,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -35414,12 +35414,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36046,12 +36046,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
